--- a/exports/FCLS_Jobber_Setup.xlsx
+++ b/exports/FCLS_Jobber_Setup.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internal Estimator" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quick Quote Matrix" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobber Category Setup" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Price Sheet" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom Fields" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tags" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer Price Sheet" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,13 +463,13 @@
   <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -526,7 +528,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Professional refresh of existing gravel driveway using AB-3 road base. Includes delivery, spreading, and grading with tracked skid steer for a clean, even finish.</t>
+          <t>Owner-operated gravel driveway refresh using tracked Bobcat equipment and AB-3 road base. Delivered, spread, graded, and crowned for a smooth, durable finish. Free quotes. Before &amp; after photos available.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -536,12 +538,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>$145.00</t>
+          <t>145.00</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -551,7 +553,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Typical residential drive 100-250 ft uses 8-18 tons. Confirm tonnage based on width/depth before quoting. Margin target 50%.</t>
+          <t>Typical residential drive 100-250 ft uses 8-18 tons. Confirm tonnage based on width/depth. Margin target 50%. Best Attachment: standard bucket. Typical project 4-8 hrs.</t>
         </is>
       </c>
     </row>
@@ -568,7 +570,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Professional spreading and grading of customer-supplied gravel using a tracked skid steer. Smooth, level finish with proper crown.</t>
+          <t>Owner-operated spreading and grading of customer-supplied gravel using tracked Bobcat equipment. Smooth, level finish with proper crown. Free quotes.</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -578,12 +580,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>$65.00</t>
+          <t>65.00</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -593,7 +595,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Lower-margin work. Only book on small jobs or when paired with other services.</t>
+          <t>Lower-margin work. Only book on small jobs or when paired with other services. Best Attachment: standard bucket.</t>
         </is>
       </c>
     </row>
@@ -610,7 +612,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Targeted pothole repair using compacted AB-3 base. Cleaned, filled, and graded for a durable patch.</t>
+          <t>Targeted pothole repair using compacted AB-3 base. Cleaned, filled, and graded for a durable patch. Tracked Bobcat equipment. Owner-operated. Free quotes.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -620,12 +622,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>$125.00</t>
+          <t>125.00</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -635,7 +637,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Bundle 4+ potholes into Pothole Package. Single-pothole minimum $185 due to mobilization.</t>
+          <t>Bundle 4+ potholes into Pothole Package. Single-pothole minimum $185 due to mobilization. Best Attachment: standard bucket. Typical 1-4 hrs.</t>
         </is>
       </c>
     </row>
@@ -652,7 +654,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Reshape and re-crown an existing gravel drive for proper drainage and a smooth ride.</t>
+          <t>Reshape and re-crown an existing gravel drive for proper drainage and a smooth ride. Tracked Bobcat equipment. Owner-operated. Free quotes.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -662,12 +664,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>$370.00 (2-hr min)</t>
+          <t>370.00</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -677,49 +679,49 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2-hr minimum. Most jobs 2-4 hrs. Push gravel-add-on at quote.</t>
+          <t>2-hr minimum on-site. Most jobs 2-4 hrs. Push gravel-add-on at quote. Best Attachment: standard bucket.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Property Cleanup</t>
+          <t>Driveway &amp; Gravel</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Brush Pile Removal - Standard</t>
+          <t>Driveway Culvert Repair</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Removal of accumulated brush, limbs, and yard debris using grapple-equipped skid steer. Clean haul-off included.</t>
+          <t>Repair, replace, or extend driveway culverts using tracked Bobcat equipment. Includes excavation, pipe work, backfill, and gravel restoration to keep your driveway draining properly. Owner-operated. Free quotes.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Per pile (pickup-truck size)</t>
+          <t>Per project</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>$275.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>850.00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Fence line cleanup; Storm debris removal</t>
+          <t>Gravel top dressing; Embankment regrade; AB-3 driveway refresh</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Confirm if customer can burn on-site (rural). Pile size verified on-site; reserve right to re-quote.</t>
+          <t>Most residential jobs $1,200-$2,500 (12-18 in HDPE, 15-20 ft span). Material pass-through plus 25-35% markup. Half day to full day typical. Best Attachment: standard bucket. Quote Confidence: Low - site visit recommended.</t>
         </is>
       </c>
     </row>
@@ -731,37 +733,37 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>General Property Cleanup</t>
+          <t>Brush Pile Removal - Standard</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Skid-steer-assisted cleanup of yard debris, fallen limbs, scrap, and accumulated material.</t>
+          <t>Owner-operated removal of accumulated brush, limbs, and yard debris using tracked Bobcat with grapple. Clean haul-off included. Free quotes. Before &amp; after photos available.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Per hour</t>
+          <t>Per pile (pickup-truck size)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>275.00</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>$625.00 (half day)</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Brush hauling; Dump fee</t>
+          <t>Fence line cleanup; Storm debris removal</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Half-day minimum recommended unless paired with another service.</t>
+          <t>Confirm if customer can burn on-site (rural). Pile size verified on-site; reserve right to re-quote. Best Attachment: grapple. Typical 2-4 hrs.</t>
         </is>
       </c>
     </row>
@@ -773,12 +775,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Storm Cleanup - Emergency Response</t>
+          <t>General Property Cleanup</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Rapid response storm debris cleanup. Tree limb removal, access clearing, debris staging or haul-off.</t>
+          <t>Owner-operated cleanup of yard debris, fallen limbs, scrap, and accumulated material using tracked Bobcat equipment. Free quotes.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -788,64 +790,64 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>$215.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>$860.00 (4-hr min)</t>
+          <t>625.00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Small tree removal; Fence line work</t>
+          <t>Brush hauling; Dump fee</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4-hr minimum. Add 25% emergency surcharge for under 48-hr response.</t>
+          <t>Half-day minimum recommended ($625) unless paired with another service. Best Attachment: grapple.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Vegetation Management</t>
+          <t>Property Cleanup</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Acreage Mowing - Tall Grass / Pasture</t>
+          <t>Storm Cleanup - Emergency Response</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Heavy-duty rotary cutting of tall grass, light brush, and overgrown pasture using skid-steer brush cutter. Suitable for grass up to 6 ft.</t>
+          <t>Rapid-response storm debris cleanup. Tree limb removal, access clearing, debris staging or haul-off using tracked Bobcat equipment. Owner-operated. Free quotes. Before &amp; after photos available.</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Per acre</t>
+          <t>Per hour</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>$195.00</t>
+          <t>215.00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>860.00</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Fence line cleanup; Tree edge cleanup</t>
+          <t>Small tree removal; Fence line work</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Hilly/wet acreage +20%. Best margin: 2+ acre flat jobs.</t>
+          <t>4-hr minimum. Add 25% emergency surcharge for under 48-hr response. Highest urgency = highest margin. Best Attachment: grapple.</t>
         </is>
       </c>
     </row>
@@ -857,37 +859,37 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Heavy Brush Cutting - Per Hour</t>
+          <t>Acreage Mowing - Tall Grass / Pasture</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Aggressive brush cutting in dense overgrown areas using heavy-duty cutter attachment. Clears saplings up to 3 in diameter.</t>
+          <t>Heavy-duty rotary cutting of tall grass, light brush, and overgrown pasture using tracked Bobcat with brush cutter. Suitable for grass up to 6 ft. Owner-operated. Free quotes.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Per hour</t>
+          <t>Per acre</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>$235.00</t>
+          <t>195.00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Stump grinding follow-up; Debris removal</t>
+          <t>Fence line cleanup; Tree edge cleanup</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Use when acre pricing won't cover density. Always quote site-unseen as range.</t>
+          <t>Hilly/wet acreage +20%. Best margin: 2+ acre flat jobs. Best Attachment: brush cutter. Typical 30-45 min per acre.</t>
         </is>
       </c>
     </row>
@@ -899,79 +901,79 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Fence Line Cleanup</t>
+          <t>Heavy Brush Cutting - Per Hour</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Restore fence lines overgrown with brush, vines, and saplings. Cleared to allow fence repair or visibility.</t>
+          <t>Aggressive brush cutting in dense overgrown areas using tracked Bobcat with heavy-duty cutter attachment. Clears saplings up to 3 in diameter. Owner-operated. Free quotes.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Per linear foot</t>
+          <t>Per hour</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>235.00</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>$750.00</t>
+          <t>850.00</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Brush haul-off; Tree removal at fence corners</t>
+          <t>Stump grinding follow-up; Debris removal</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Density-based pricing. Light $4.50/ft, Medium $7.50/ft, Heavy $14/ft.</t>
+          <t>Use when acre pricing won't cover density. Always quote site-unseen as range. Best Attachment: brush cutter. Higher minimum due to attachment wear.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Tree &amp; Stump</t>
+          <t>Vegetation Management</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Stump Grinding - Standard</t>
+          <t>Fence Line Cleanup</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Stump ground to 4-6 in below grade using skid-steer stump grinder. Chips left on-site or hauled per request.</t>
+          <t>Restore fence lines overgrown with brush, vines, and saplings. Cleared to allow fence repair or visibility. Tracked Bobcat equipment. Owner-operated. Free quotes. Before &amp; after photos available.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Per inch of diameter</t>
+          <t>Per linear foot</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>$7.00</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>750.00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Chip haul-off; Soil and seed restoration</t>
+          <t>Brush haul-off; Tree removal at fence corners</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Multi-stump discount: 10% off when 5+ stumps booked together; 15% off for 10+.</t>
+          <t>Density-based pricing. Light $4.50/ft, Medium $7.50/ft, Heavy $14/ft. Best Attachment: brush cutter or grapple.</t>
         </is>
       </c>
     </row>
@@ -983,79 +985,79 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Small Tree Removal</t>
+          <t>Stump Grinding - Standard</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Removal of small trees up to 25 ft tall in accessible locations. Includes felling, sectioning, and stacking or haul-off.</t>
+          <t>Stump ground to 4-6 in below grade using tracked Bobcat with stump grinder. Chips left on-site or hauled per request. Owner-operated. Free quotes.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Per tree</t>
+          <t>Per inch of diameter</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>$385.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Stump grinding; Brush removal</t>
+          <t>Chip haul-off; Soil and seed restoration</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Typical 6-12 in trunk. No tall climbing. Refer to arborist for trees with overhead hazards or near structures.</t>
+          <t>Multi-stump discount: 10% off when 5+ stumps booked together; 15% off for 10+. Best Attachment: stump grinder. Typical 15-45 min per stump.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Grading &amp; Dirt Work</t>
+          <t>Tree &amp; Stump</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Light Grading</t>
+          <t>Small Tree Removal</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Surface grading and leveling for yards, pads, lots, and driveway approaches.</t>
+          <t>Removal of small trees up to 25 ft tall in accessible locations using tracked Bobcat equipment. Includes felling, sectioning, and stacking or haul-off. Owner-operated. Free quotes.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Per hour</t>
+          <t>Per tree</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>385.00</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>$740.00 (4-hr min)</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Topsoil spread; Seed prep</t>
+          <t>Stump grinding; Brush removal</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Add Harley rake premium ($225/hr) for finish work.</t>
+          <t>Typical 6-12 in trunk. No tall climbing. Refer to arborist for trees with overhead hazards or near structures. Best Attachment: grapple plus chainsaw.</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1069,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Dirt Work - Excavation &amp; Fill</t>
+          <t>Light Grading</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>General dirt work including small excavation, fill, leveling, and pad prep.</t>
+          <t>Surface grading and leveling for yards, pads, lots, and driveway approaches. Tracked Bobcat equipment.</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1082,22 +1084,22 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>$195.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>740.00</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Material delivery; Drainage tie-in</t>
+          <t>Topsoil spread; Seed prep</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Confirm utility locates (Kansas One-Call) before quoting.</t>
+          <t>4-hr minimum recommended. Add Harley rake premium ($225/hr) for finish work. Best Attachment: standard bucket or Harley rake.</t>
         </is>
       </c>
     </row>
@@ -1109,79 +1111,79 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Minor Drainage Correction</t>
+          <t>Dirt Work - Excavation &amp; Fill</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Targeted correction of standing-water issues - swale shaping, surface drainage, low-spot fill, or culvert assistance.</t>
+          <t>General dirt work including small excavation, fill, leveling, and pad prep using tracked Bobcat equipment.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Per project</t>
+          <t>Per hour</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>$1,450.00</t>
+          <t>195.00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Material supply; French drain rock</t>
+          <t>Material delivery; Drainage tie-in</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Walk site before quoting. Avoid jobs requiring engineered designs.</t>
+          <t>Always confirm utility locates (Kansas One-Call) before quoting. Best Attachment: standard bucket. Utility Locate Required.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Grading &amp; Dirt Work</t>
+          <t>Specialty / Project Services</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Material Spreading - Mulch / Topsoil / Decorative Rock</t>
+          <t>Minor Drainage Correction</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Bulk material delivery and professional spreading using skid steer.</t>
+          <t>Project-style correction of standing-water issues - swale shaping, surface drainage, or low-spot fill - using tracked Bobcat equipment.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Per ton or yard</t>
+          <t>Per project</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>$55.00 per ton or $65.00 per yard</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Light grading; Edge prep</t>
+          <t>Material supply; French drain rock; Gravel top dressing</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Charge separately for material + spread. Always quote material with markup.</t>
+          <t>Secondary service - do not lead residential marketing with this. Walk site before quoting. Avoid jobs requiring engineered designs. Quote Confidence: Low - site visit required.</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1200,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Demolition and haul-off of sheds, small outbuildings, decks, fences, and accessory structures.</t>
+          <t>Demolition and haul-off of sheds, small outbuildings, decks, fences, and accessory structures. Tracked Bobcat equipment.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1208,12 +1210,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>$1,850.00</t>
+          <t>1850.00</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>$850.00</t>
+          <t>850.00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1223,7 +1225,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Quote on site only. Confirm asbestos-free for pre-1980 structures.</t>
+          <t>Quote on site only. Confirm asbestos-free for pre-1980 structures. Best Attachment: grapple. Quote Confidence: Low.</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1242,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Removal and haul-off of existing fencing including posts.</t>
+          <t>Removal and haul-off of existing fencing including posts. Tracked Bobcat equipment.</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1250,12 +1252,12 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>$6.50</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1265,7 +1267,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Concrete-set posts +$3/ft. Barbed wire +$2/ft.</t>
+          <t>Concrete-set posts +$3/ft. Barbed wire +$2/ft. Best Attachment: grapple.</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1284,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Tracked skid steer with experienced operator for hourly work. Versatile, productive, and efficient for a wide range of property tasks.</t>
+          <t>Tracked Bobcat skid steer with experienced owner-operator for hourly work. Versatile, productive, and efficient for a wide range of property tasks. Free quotes.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1292,12 +1294,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>$370.00 (2-hr min)</t>
+          <t>370.00</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1324,7 +1326,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Half-day skid steer service - ideal for medium cleanup, grading, or material spreading projects.</t>
+          <t>Half-day tracked Bobcat skid steer service - ideal for medium cleanup, grading, or material spreading projects. Owner-operated. Free quotes.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1334,12 +1336,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>$625.00</t>
+          <t>625.00</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>$625.00</t>
+          <t>625.00</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1366,7 +1368,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Full-day skid steer service for larger property projects.</t>
+          <t>Full-day tracked Bobcat skid steer service for larger property projects. Owner-operated. Free quotes.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1376,12 +1378,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>$1,200.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>$1,200.00</t>
+          <t>1200.00</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1408,7 +1410,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Up to 2 brush piles removed, 3 hours skid steer with grapple, light fence-line touch-up (up to 200 ft), and property debris haul-off (1 trailer load).</t>
+          <t>Up to 2 brush piles removed, 3 hours tracked Bobcat with grapple, light fence-line touch-up (up to 200 ft), and property debris haul-off (1 trailer load). Owner-operated. Free quotes.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1418,12 +1420,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>$1,495.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>$1,495.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -1450,7 +1452,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Up to 12 tons AB-3 delivered and spread, pothole repair (up to 6 holes), light grading and re-crown, edge re-establishment.</t>
+          <t>Up to 12 tons AB-3 delivered and spread, pothole repair (up to 6 holes), light grading and re-crown, edge re-establishment. Tracked Bobcat equipment. Owner-operated. Free quotes. Before &amp; after photos available.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1460,12 +1462,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>$1,995.00</t>
+          <t>1995.00</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>$1,995.00</t>
+          <t>1995.00</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1492,7 +1494,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Up to 500 linear feet of fence line cleared (medium density), brush haul-off or push-to-burn-pile, corner tree/stump prep (up to 3 stumps under 12 in), 1 hour finish-grade touch-up.</t>
+          <t>Up to 500 linear feet of fence line cleared (medium density), brush haul-off or push-to-burn-pile, corner tree/stump prep (up to 3 stumps under 12 in), 1 hour finish-grade touch-up. Tracked Bobcat equipment.</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1502,12 +1504,12 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>$4,250.00</t>
+          <t>4250.00</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>$4,250.00</t>
+          <t>4250.00</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -1534,7 +1536,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>6 hours skid steer with grapple, up to 3 brush piles consolidated/removed, 1 small tree removal (up to 12 in trunk, accessible), driveway clearing and access restoration.</t>
+          <t>6 hours tracked Bobcat with grapple, up to 3 brush piles consolidated/removed, 1 small tree removal (up to 12 in trunk, accessible), driveway clearing and access restoration. Owner-operated. Free quotes.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1544,12 +1546,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>$1,950.00</t>
+          <t>1950.00</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>$1,950.00</t>
+          <t>1950.00</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1576,7 +1578,7 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Up to 5 acres rotary mowing, fence-line touch-up (up to 250 ft), one brush pile pushed/cleared.</t>
+          <t>Up to 5 acres rotary mowing, fence-line touch-up (up to 250 ft), one brush pile pushed/cleared. Tracked Bobcat equipment. Owner-operated.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1586,12 +1588,12 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>$1,375.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>$1,375.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -1618,7 +1620,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Three scheduled maintenance visits during the May-October season. Each visit includes up to 5 acres mowed, 250 ft fence-line touch-up, and one brush pile cleared.</t>
+          <t>Three scheduled maintenance visits during the May-October season. Each visit includes up to 5 acres mowed, 250 ft fence-line touch-up, and one brush pile cleared. Tracked Bobcat equipment.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1628,12 +1630,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>$3,750.00</t>
+          <t>3750.00</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>$3,750.00</t>
+          <t>3750.00</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1658,19 +1660,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
-    <col width="60" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="9" max="9"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="43" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1711,15 +1717,35 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Attachment Needed</t>
+          <t>Best Attachment</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Typical Production Time</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Difficulty Modifier</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Quote Confidence</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Photo Potential</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Material Notes</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Margin Notes</t>
         </is>
@@ -1743,22 +1769,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$115.00</t>
+          <t>115.00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>$145.00</t>
+          <t>145.00</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1768,10 +1794,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>4-8 hrs / 100-250 ft drive</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>1.0 easy / 1.10 medium / 1.20 hard</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>High - remote OK with photos and length</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>AB-3 road base; supplier $24-$32/ton + delivery</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Target 50% margin. Highest repeat residential service.</t>
         </is>
@@ -1795,22 +1841,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>$45.00</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>$65.00</t>
+          <t>65.00</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>$85.00</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1820,10 +1866,30 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>2-4 hrs typical</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>1.0 easy / 1.10 medium</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
           <t>Customer-supplied material</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Low margin (30-40%). Bundle only.</t>
         </is>
@@ -1847,22 +1913,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>$125.00</t>
+          <t>125.00</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>$225.00</t>
+          <t>225.00</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1872,10 +1938,30 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>1-4 hrs / 2-10 holes</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1.0 standard</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>AB-3 base, minimal tonnage</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Very high margin (60-70%). Fastest cash flow.</t>
         </is>
@@ -1889,7 +1975,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Driveway grading &amp; reshaping</t>
+          <t>Driveway grading and reshaping</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1899,22 +1985,22 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>$165.00</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>$215.00</t>
+          <t>215.00</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>$370.00</t>
+          <t>370.00</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1924,10 +2010,30 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>No material (unless top dressing added)</t>
+          <t>2-4 hrs typical</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>1.0 easy / 1.10 medium</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>No material unless top dressing added</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>Medium-high margin. Pair with gravel for higher ticket.</t>
         </is>
@@ -1936,52 +2042,72 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Property Cleanup</t>
+          <t>Driveway &amp; Gravel</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Property cleanup</t>
+          <t>Driveway culvert repair</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Per hour</t>
+          <t>Per project</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$165.00</t>
+          <t>850.00</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>$225.00</t>
+          <t>4500.00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>850.00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Grapple</t>
+          <t>Standard bucket</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Dump fees pass-through + 20% handling</t>
+          <t>Half day to 1 full day</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Medium margin (40-50%). Volume play with repeat potential.</t>
+          <t>1.10 medium / 1.20 hard / 1.30 deep install</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>HDPE pipe $15-$30/ft; gravel restoration; markup material 25-35%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Medium-high margin. Confirm pipe size and condition on-site.</t>
         </is>
       </c>
     </row>
@@ -1993,32 +2119,32 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Brush pile removal</t>
+          <t>Property cleanup</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Per pickup-truck pile</t>
+          <t>Per hour</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>$275.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>$425.00</t>
+          <t>225.00</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -2028,12 +2154,32 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Confirm burn-on-site option (rural) for higher margin</t>
+          <t>Half-day to full-day typical</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>High margin (55-65%). On-site burn = pure margin.</t>
+          <t>1.0 standard</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Dump fees pass-through + 20% handling</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Medium margin (40-50%). Volume play with repeat potential.</t>
         </is>
       </c>
     </row>
@@ -2045,32 +2191,32 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Storm cleanup (emergency)</t>
+          <t>Brush pile removal</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Per hour</t>
+          <t>Per pickup-truck pile</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>$215.00</t>
+          <t>275.00</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>$275.00</t>
+          <t>425.00</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>$860.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2080,64 +2226,104 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Variable dump fees</t>
+          <t>2-4 hrs per pile</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Very high margin (65-75%). Add 25% emergency surcharge.</t>
+          <t>1.0 standard</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Confirm burn-on-site option (rural) for higher margin</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>High margin (55-65%). On-site burn = pure margin.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Vegetation Management</t>
+          <t>Property Cleanup</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Acreage mowing</t>
+          <t>Storm cleanup (emergency)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Per acre</t>
+          <t>Per hour</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>$145.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>$195.00</t>
+          <t>215.00</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>$295.00</t>
+          <t>275.00</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>860.00</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Brush cutter</t>
+          <t>Grapple</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Blade wear $35/hr reserve</t>
+          <t>4-8 hrs typical</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Medium margin. Recurring seasonal revenue.</t>
+          <t>1.10-1.30 by site condition</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required; 4-hr min</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Variable dump fees</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Very high margin (65-75%). Add 25% emergency surcharge.</t>
         </is>
       </c>
     </row>
@@ -2149,32 +2335,32 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Brush cutting (heavy)</t>
+          <t>Acreage mowing</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Per hour</t>
+          <t>Per acre</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$215.00</t>
+          <t>145.00</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>$235.00</t>
+          <t>195.00</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>$275.00</t>
+          <t>295.00</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2184,12 +2370,32 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>High blade wear</t>
+          <t>30 min/acre light, 45 min/acre tall</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Medium-high margin. Always quote site-unseen as range.</t>
+          <t>1.0 flat / 1.20 hilly or wet</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>High - remote OK with acreage and density</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Blade wear $35/hr reserve</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Medium margin. Recurring seasonal revenue.</t>
         </is>
       </c>
     </row>
@@ -2201,99 +2407,139 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Fence line cleanup</t>
+          <t>Brush cutting (heavy)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Per linear foot</t>
+          <t>Per hour</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>$4.50</t>
+          <t>215.00</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>$7.50</t>
+          <t>235.00</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>$14.00</t>
+          <t>275.00</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>$750.00</t>
+          <t>850.00</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Brush cutter or grapple</t>
+          <t>Brush cutter</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Density-based: Light 4.50, Medium 7.50, Heavy 14</t>
+          <t>Half-day to full-day</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>High margin (50-60%). Project-style work.</t>
+          <t>1.10-1.25 by density</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>High blade wear</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Medium-high margin. Higher minimum due to attachment wear.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Tree &amp; Stump</t>
+          <t>Vegetation Management</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Stump grinding</t>
+          <t>Fence line cleanup</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Per inch diameter</t>
+          <t>Per linear foot</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$5.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>$7.00</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>$11.00</t>
+          <t>14.00</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>750.00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Stump grinder</t>
+          <t>Brush cutter or grapple</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>$30/hr wear reserve plus tooth pass-through</t>
+          <t>60-120 ft per hour by density</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Very high margin (60-70%). Track tooth wear carefully.</t>
+          <t>1.0 light / 1.10 medium / 1.20 heavy</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Density-based: Light 4.50, Medium 7.50, Heavy 14.00</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>High margin (50-60%). Project-style work.</t>
         </is>
       </c>
     </row>
@@ -2305,99 +2551,139 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Small tree removal</t>
+          <t>Stump grinding</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Per tree</t>
+          <t>Per inch diameter</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>$385.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>$850.00</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Grapple + chainsaw</t>
+          <t>Stump grinder</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Brush haul-off if no on-site burn</t>
+          <t>15-45 min per stump by diameter</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Medium-high margin (45-55%). Bundle with stump grinding.</t>
+          <t>1.0 standard / 1.20 root-bound</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>High - remote OK with diameter and count</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>$30/hr wear reserve plus tooth pass-through</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Very high margin (60-70%). Track tooth wear carefully.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Grading &amp; Dirt Work</t>
+          <t>Tree &amp; Stump</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Light grading</t>
+          <t>Small tree removal</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Per hour</t>
+          <t>Per tree</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$165.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>385.00</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>$215.00</t>
+          <t>850.00</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Standard bucket or Harley rake</t>
+          <t>Grapple plus chainsaw</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Topsoil if seeding follow-up</t>
+          <t>30-90 min per tree</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Medium-high margin. Pair with material.</t>
+          <t>1.10-1.30 by access</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Brush haul-off if no on-site burn</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Medium-high margin (45-55%). Bundle with stump grinding.</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2695,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Dirt work</t>
+          <t>Light grading</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -2419,37 +2705,57 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>$175.00</t>
+          <t>165.00</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>$195.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>$235.00</t>
+          <t>215.00</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>740.00</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Standard bucket</t>
+          <t>Standard bucket or Harley rake</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Fill dirt or topsoil pass-through</t>
+          <t>4-8 hrs typical</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Medium margin (40-50%). Confirm utility locates.</t>
+          <t>1.0 easy / 1.10 medium</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Topsoil if seeding follow-up</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Medium-high margin. Pair with material.</t>
         </is>
       </c>
     </row>
@@ -2461,32 +2767,32 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Minor drainage correction</t>
+          <t>Dirt work</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Per project</t>
+          <t>Per hour</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>$1,450.00</t>
+          <t>195.00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>$3,200.00</t>
+          <t>235.00</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2496,49 +2802,69 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1 in clean rock for French drains; ABC mix</t>
+          <t>Half-day to full-day</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Medium margin. Avoid engineered work.</t>
+          <t>1.10 medium / 1.20 hard</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Fill dirt or topsoil pass-through</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Medium margin (40-50%). Confirm utility locates.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Grading &amp; Dirt Work</t>
+          <t>Specialty / Project Services</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Material spreading</t>
+          <t>Minor drainage correction</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Per ton</t>
+          <t>Per project</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>$35.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>$55.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>$75.00</t>
+          <t>3200.00</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -2548,116 +2874,176 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Material at delivered cost + 25-35% markup</t>
+          <t>Half-day to 1 full day</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Low-medium margin (30-40%). Bundle only.</t>
+          <t>1.10-1.30 by site</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>1 in clean rock for French drains; ABC mix</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Medium margin. Avoid engineered work. Secondary service.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Demolition</t>
+          <t>Internal / Bundled</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Small demolition</t>
+          <t>Material spreading (internal cost component)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Per project</t>
+          <t>Per ton</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$850.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>$2,450.00</t>
+          <t>55.00</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>$6,500.00</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>$850.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Grapple</t>
+          <t>Standard bucket</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Construction debris dump $185-$385 per load</t>
+          <t>1-3 hrs typical</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Medium-high margin. Quote on site only.</t>
+          <t>1.0 standard</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>n/a - bundled into other services</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Material at delivered cost + 25-35% markup</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Low-medium margin (30-40%). No longer offered standalone to customers; bundled inside Driveway Refresh and Light Grading.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Hourly / Skid Steer</t>
+          <t>Demolition</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Loader work</t>
+          <t>Small demolition</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Per hour</t>
+          <t>Per project</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>$165.00</t>
+          <t>850.00</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>2450.00</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>$215.00</t>
+          <t>6500.00</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>850.00</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Standard bucket or forks</t>
+          <t>Grapple</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Light material handling</t>
+          <t>Half-day to full-day per structure</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Medium margin. Filler work.</t>
+          <t>1.10-1.30 by access</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Construction debris dump $185-$385 per load</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Medium-high margin. Quote on site only.</t>
         </is>
       </c>
     </row>
@@ -2669,45 +3055,137 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>Loader work</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Per hour</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>165.00</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>185.00</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>215.00</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>450.00</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Standard bucket or forks</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1.0 standard</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Light material handling</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Medium margin. Filler work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Hourly / Skid Steer</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>Skid steer hourly (general)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Per hour</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>$165.00</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>$185.00</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>$215.00</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>$450.00</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>165.00</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>185.00</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>215.00</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>370.00</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>Standard bucket</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>2-hr minimum on-site</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>1.0 standard</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>Attachment premium per Section 8</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="N21" s="3" t="inlineStr">
         <is>
           <t>Medium margin. 2-hr minimum on-site.</t>
         </is>
@@ -2724,14 +3202,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="53" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2757,6 +3238,21 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Best Attachment</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Typical Production Time</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Quote Confidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
@@ -2779,12 +3275,27 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Minimum charge applies. AB-3, 2 in depth, 10 ft wide.</t>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>AB-3, 2 in depth, 10 ft wide. Minimum charge applies.</t>
         </is>
       </c>
     </row>
@@ -2806,10 +3317,25 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>$1,150.00 - $1,450.00</t>
+          <t>1,150.00 - 1,450.00</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>3-4 hrs</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>AB-3, 2 in depth, 10 ft wide.</t>
         </is>
@@ -2833,10 +3359,25 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>$1,650.00 - $2,150.00</t>
+          <t>1,650.00 - 2,150.00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>AB-3, 2 in depth, 10 ft wide.</t>
         </is>
@@ -2860,10 +3401,25 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>$2,150.00 - $2,850.00</t>
+          <t>2,150.00 - 2,850.00</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>5-7 hrs</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>AB-3, 2 in depth, 10 ft wide.</t>
         </is>
@@ -2887,10 +3443,25 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>$3,150.00 - $4,300.00</t>
+          <t>3,150.00 - 4,300.00</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6-8 hrs</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>AB-3, 2 in depth, 10 ft wide.</t>
         </is>
@@ -2914,10 +3485,25 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>$5,200.00 - $7,200.00</t>
+          <t>5,200.00 - 7,200.00</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>1 full day</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>AB-3, 2 in depth, 10 ft wide.</t>
         </is>
@@ -2941,10 +3527,25 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>$10,400.00 - $14,500.00</t>
+          <t>10,400.00 - 14,500.00</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1.5-2 days</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>AB-3, 2 in depth, 10 ft wide. Add 20% for 12-ft drives. Add 50% for 4-in rebuild.</t>
         </is>
@@ -2968,10 +3569,25 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>30 min/acre</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Minimum charge applies.</t>
         </is>
@@ -2995,14 +3611,25 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>$175.00</t>
+          <t>175.00</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Per acre rate; minimum may apply.</t>
-        </is>
-      </c>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30 min/acre</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3022,10 +3649,25 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>$325.00</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
+          <t>325.00</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>30 min/acre</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3045,10 +3687,25 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>$475.00</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>475.00</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30 min/acre</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3068,10 +3725,25 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>$775.00</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr"/>
+          <t>775.00</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>30 min/acre</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3091,10 +3763,25 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>$1,450.00</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>1,450.00</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30 min/acre</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3114,10 +3801,25 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>$2,750.00</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr"/>
+          <t>2,750.00</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>30 min/acre</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3137,10 +3839,25 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>45 min/acre</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Minimum charge applies.</t>
         </is>
@@ -3164,10 +3881,25 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>$235.00</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr"/>
+          <t>235.00</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>45 min/acre</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3187,10 +3919,25 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>$425.00</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr"/>
+          <t>425.00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>45 min/acre</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3210,10 +3957,25 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>$625.00</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
+          <t>625.00</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>45 min/acre</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3233,10 +3995,25 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>$1,050.00</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
+          <t>1,050.00</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>45 min/acre</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -3256,10 +4033,25 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>$1,975.00</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
+          <t>1,975.00</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>45 min/acre</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -3279,10 +4071,25 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>$3,750.00</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr"/>
+          <t>3,750.00</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>45 min/acre</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -3302,10 +4109,25 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>$650.00</t>
+          <t>650.00</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>60-90 min/acre</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Rural minimum applies.</t>
         </is>
@@ -3329,10 +4151,25 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>$385.00</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
+          <t>385.00</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>60-90 min/acre</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -3352,10 +4189,25 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>$725.00</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr"/>
+          <t>725.00</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>60-90 min/acre</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -3375,10 +4227,25 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>$1,050.00</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr"/>
+          <t>1,050.00</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>60-90 min/acre</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -3398,10 +4265,25 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>$1,725.00</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr"/>
+          <t>1,725.00</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>60-90 min/acre</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -3421,10 +4303,25 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>$3,250.00</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr"/>
+          <t>3,250.00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>60-90 min/acre</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -3444,10 +4341,25 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>$6,250.00</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
+          <t>6,250.00</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>60-90 min/acre</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3467,10 +4379,25 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>$4.50/ft ($750 min)</t>
+          <t>4.50/ft (750.00 min)</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Light: grass, vines, growth under 1 in.</t>
         </is>
@@ -3494,10 +4421,25 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>$7.50/ft ($750 min)</t>
+          <t>7.50/ft (750.00 min)</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>Medium: mixed brush, woody growth up to 2 in.</t>
         </is>
@@ -3521,10 +4463,25 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>$14.00/ft ($750 min)</t>
+          <t>14.00/ft (750.00 min)</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Heavy: saplings 2-3 in, dense undergrowth.</t>
         </is>
@@ -3548,10 +4505,25 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>$4.50/ft</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr"/>
+          <t>4.50/ft</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3571,10 +4543,25 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>$7.50/ft</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr"/>
+          <t>7.50/ft</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -3594,10 +4581,25 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>$14.00/ft</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr"/>
+          <t>14.00/ft</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3617,10 +4619,25 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>$4.25/ft</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr"/>
+          <t>4.25/ft</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -3640,10 +4657,25 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>$7.00/ft</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr"/>
+          <t>7.00/ft</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3663,10 +4695,25 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>$13.00/ft</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr"/>
+          <t>13.00/ft</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -3686,10 +4733,25 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>$3.95/ft</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr"/>
+          <t>3.95/ft</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3709,10 +4771,25 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>$6.50/ft</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr"/>
+          <t>6.50/ft</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -3732,10 +4809,25 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>$12.00/ft</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr"/>
+          <t>12.00/ft</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3760,6 +4852,21 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
+          <t>Brush cutter / grapple</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>60-120 ft/hr by density</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Low - site visit</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
           <t>Walk site before quoting.</t>
         </is>
       </c>
@@ -3782,10 +4889,25 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Stump grinder</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>15-30 min</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Minimum visit charge.</t>
         </is>
@@ -3809,10 +4931,25 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Stump grinder</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>15-30 min</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Minimum visit charge.</t>
         </is>
@@ -3836,10 +4973,25 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Stump grinder</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>15-30 min</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Minimum visit charge.</t>
         </is>
@@ -3863,10 +5015,25 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>$215.00</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr"/>
+          <t>215.00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Stump grinder</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>30-45 min</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -3886,10 +5053,25 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>$285.00</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr"/>
+          <t>285.00</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Stump grinder</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>30-45 min</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3909,10 +5091,25 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>$355.00</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
+          <t>355.00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Stump grinder</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>30-45 min</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -3932,10 +5129,25 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>$425.00</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr"/>
+          <t>425.00</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Stump grinder</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>30-45 min</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3955,10 +5167,25 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>$565.00</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr"/>
+          <t>565.00</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Stump grinder</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>30-45 min</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
@@ -3983,6 +5210,21 @@
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
+          <t>Stump grinder</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>30-45 min</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>Low - site visit</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
           <t>Multi-pass or large grinder.</t>
         </is>
       </c>
@@ -4010,6 +5252,21 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
+          <t>Stump grinder</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Bulk visit</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
           <t>Discount applied when 5+ stumps booked together.</t>
         </is>
       </c>
@@ -4037,6 +5294,21 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
+          <t>Stump grinder</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Bulk visit</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
           <t>Discount applied when 10+ stumps booked together.</t>
         </is>
       </c>
@@ -4059,10 +5331,25 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>$275.00</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>275.00</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -4082,10 +5369,25 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
         <is>
           <t>Minimum charge.</t>
         </is>
@@ -4109,10 +5411,25 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>$475.00</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
+          <t>475.00</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Half-day</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -4132,10 +5449,25 @@
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>$325.00</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr"/>
+          <t>325.00</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Half-day</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4155,10 +5487,25 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>$850.00</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr"/>
+          <t>850.00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Full-day</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
@@ -4178,10 +5525,25 @@
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>$585.00</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr"/>
+          <t>585.00</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Full-day</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4204,7 +5566,22 @@
           <t>Quote on-site</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Low - site visit</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
@@ -4224,10 +5601,25 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>$850.00 - $1,250.00</t>
+          <t>850.00 - 1,250.00</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Half day to full day</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
         <is>
           <t>Half-day work.</t>
         </is>
@@ -4251,10 +5643,25 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>$1,450.00 - $2,250.00</t>
+          <t>1,450.00 - 2,250.00</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Half day to full day</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Most common.</t>
         </is>
@@ -4278,10 +5685,25 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>$2,250.00 - $3,500.00</t>
+          <t>2,250.00 - 3,500.00</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Half day to full day</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
         <is>
           <t>Often full day.</t>
         </is>
@@ -4305,10 +5727,25 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>$4,500.00 - $7,500.00</t>
+          <t>4,500.00 - 7,500.00</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Half day to full day</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Quote on-site.</t>
         </is>
@@ -4332,10 +5769,25 @@
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>$850.00 - $1,650.00</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr"/>
+          <t>850.00 - 1,650.00</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Half day to full day</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4355,10 +5807,25 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>$1,650.00 - $2,950.00</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr"/>
+          <t>1,650.00 - 2,950.00</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Half day to full day</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
@@ -4378,10 +5845,25 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>$5.50 - $7.50/ft</t>
+          <t>5.50 - 7.50/ft</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H67" s="3" t="inlineStr">
         <is>
           <t>Includes haul-off.</t>
         </is>
@@ -4405,10 +5887,25 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>$6.50 - $9.50/ft</t>
+          <t>6.50 - 9.50/ft</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Includes haul-off.</t>
         </is>
@@ -4432,10 +5929,25 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>$4.00 - $8.00/sq ft</t>
+          <t>4.00 - 8.00/sq ft</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Grapple</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H69" s="3" t="inlineStr">
         <is>
           <t>Plus dump fee.</t>
         </is>
@@ -4459,10 +5971,25 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>$185.00</t>
+          <t>185.00</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Mobilization-driven minimum.</t>
         </is>
@@ -4486,10 +6013,25 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>$450.00</t>
+          <t>450.00</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>1-4 hrs</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
         <is>
           <t>Most common residential.</t>
         </is>
@@ -4513,10 +6055,25 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>$850.00</t>
+          <t>850.00</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Half day</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Half-day equivalent.</t>
         </is>
@@ -4540,10 +6097,25 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>$1,450.00</t>
+          <t>1,450.00</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>1-4 hrs</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H73" s="3" t="inlineStr">
         <is>
           <t>Includes light grading touch-up.</t>
         </is>
@@ -4570,7 +6142,22 @@
           <t>Refer to Driveway Refresh</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>1-4 hrs</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>High - remote OK</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -4590,10 +6177,25 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>$185.00 - $285.00</t>
+          <t>185.00 - 285.00</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Grapple plus chainsaw</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>30-60 min</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H75" s="3" t="inlineStr">
         <is>
           <t>Multi-tree discount available.</t>
         </is>
@@ -4617,10 +6219,25 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>$285.00 - $485.00</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr"/>
+          <t>285.00 - 485.00</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Grapple plus chainsaw</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>60-90 min</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -4640,10 +6257,25 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>$485.00 - $725.00</t>
+          <t>485.00 - 725.00</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Grapple plus chainsaw</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>60-90 min</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
         <is>
           <t>Most common quote.</t>
         </is>
@@ -4667,10 +6299,25 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>$725.00 - $1,150.00</t>
+          <t>725.00 - 1,150.00</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Grapple plus chainsaw</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>60-90 min</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Push-over candidates if open area.</t>
         </is>
@@ -4694,10 +6341,25 @@
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>$1,150.00 - $1,850.00</t>
+          <t>1,150.00 - 1,850.00</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Grapple plus chainsaw</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>60-90 min</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Medium - photos required</t>
+        </is>
+      </c>
+      <c r="H79" s="3" t="inlineStr">
         <is>
           <t>Refer if hazardous.</t>
         </is>
@@ -4726,7 +6388,190 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
+          <t>Grapple plus chainsaw</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>60-90 min</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Low - refer</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
           <t>Not offered by FCLS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Driveway Culvert Repair</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Small repair / partial replacement</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Re-set existing pipe, minor regrade</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>850.00 - 1,200.00</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>Half-day</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>Material pass-through plus 25-35% markup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Driveway Culvert Repair</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Standard 12-18 in residential culvert (15-20 ft span)</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Full pipe replacement, backfill, gravel restoration</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>1,200.00 - 2,500.00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Half-day to 1 full day</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Material pass-through plus 25-35% markup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Driveway Culvert Repair</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Culvert extension or enlargement</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>New pipe + headwall work</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>2,200.00 - 3,500.00</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>1 full day</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>Material pass-through plus 25-35% markup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Driveway Culvert Repair</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Large or deep install</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Quote on-site; embankment work</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>3,500.00 - 4,500.00+</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Standard bucket</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>1-2 full days</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Low - site visit required</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Material pass-through plus 25-35% markup.</t>
         </is>
       </c>
     </row>
@@ -4745,8 +6590,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="56" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4828,16 +6673,16 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Property Cleanup</t>
+          <t>Driveway &amp; Gravel</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Brush Pile Removal - Standard</t>
+          <t>Driveway Culvert Repair</t>
         </is>
       </c>
     </row>
@@ -4852,7 +6697,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>General Property Cleanup</t>
+          <t>Brush Pile Removal - Standard</t>
         </is>
       </c>
     </row>
@@ -4867,22 +6712,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Storm Cleanup - Emergency Response</t>
+          <t>General Property Cleanup</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Vegetation Management</t>
+          <t>Property Cleanup</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Acreage Mowing - Tall Grass / Pasture</t>
+          <t>Storm Cleanup - Emergency Response</t>
         </is>
       </c>
     </row>
@@ -4897,7 +6742,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Heavy Brush Cutting - Per Hour</t>
+          <t>Acreage Mowing - Tall Grass / Pasture</t>
         </is>
       </c>
     </row>
@@ -4912,22 +6757,22 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Fence Line Cleanup</t>
+          <t>Heavy Brush Cutting - Per Hour</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Tree &amp; Stump</t>
+          <t>Vegetation Management</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Stump Grinding - Standard</t>
+          <t>Fence Line Cleanup</t>
         </is>
       </c>
     </row>
@@ -4942,22 +6787,22 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Small Tree Removal</t>
+          <t>Stump Grinding - Standard</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Grading &amp; Dirt Work</t>
+          <t>Tree &amp; Stump</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Light Grading</t>
+          <t>Small Tree Removal</t>
         </is>
       </c>
     </row>
@@ -4972,7 +6817,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Dirt Work - Excavation &amp; Fill</t>
+          <t>Light Grading</t>
         </is>
       </c>
     </row>
@@ -4987,28 +6832,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Minor Drainage Correction</t>
+          <t>Dirt Work - Excavation &amp; Fill</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Grading &amp; Dirt Work</t>
+          <t>Specialty / Project Services</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Material Spreading - Mulch / Topsoil / Decorative Rock</t>
+          <t>Minor Drainage Correction</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -5023,7 +6868,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -5038,7 +6883,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
@@ -5053,7 +6898,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
@@ -5068,7 +6913,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
@@ -5083,7 +6928,7 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
@@ -5098,7 +6943,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
@@ -5113,7 +6958,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
@@ -5128,7 +6973,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
@@ -5143,7 +6988,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -5158,7 +7003,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
@@ -5182,536 +7027,1023 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Custom Field</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Pricing</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Minimum / Notes</t>
+          <t>Options</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Purpose</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gravel driveway refresh</t>
+          <t>Access Difficulty</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>From $145 per ton applied</t>
+          <t>Dropdown</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>$650 minimum. AB-3 road base.</t>
+          <t>Easy / Medium / Hard / Severe</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Drives the difficulty modifier on internal pricing.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Gravel spread (customer-supplied)</t>
+          <t>Ground Conditions</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>$65 per ton</t>
+          <t>Dropdown</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>$450 minimum.</t>
+          <t>Dry / Soft / Saturated / Frozen</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Drives reschedule risk and equipment selection.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Pothole repair (single)</t>
+          <t>Estimated Tons</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>$185</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Mobilization-driven minimum.</t>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Driveway and material work.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Pothole repair (2-4 holes)</t>
+          <t>Estimated Dump Loads</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>$450</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Most common residential.</t>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr"/>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Brush, demo, cleanup pricing.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Pothole repair (5-10 holes)</t>
+          <t>Travel Zone</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>$850</t>
+          <t>Dropdown</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Half-day equivalent.</t>
+          <t>0-25 / 25-40 / 40-60 / 60+ mi</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Drives mobilization fee.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Pothole repair (11-20 holes)</t>
+          <t>Attachment Needed</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>$1,450</t>
+          <t>Dropdown</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Includes light grading touch-up.</t>
+          <t>Bucket / Grapple / Brush Cutter / Harley Rake / Stump Grinder / Auger / Forks</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Schedules the right attachment for the job.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Driveway grading &amp; reshaping</t>
+          <t>Utility Locate Required</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>$185 per hour</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2-hour minimum.</t>
+          <t>Yes / No</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Triggers Kansas One-Call.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Brush pile removal</t>
+          <t>Photos Uploaded</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>From $275 per pile</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Rural burn option from $185.</t>
+          <t>Yes / No</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Drives quote confidence.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>General property cleanup</t>
+          <t>Customer Priority</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>$185 per hour</t>
+          <t>Dropdown</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Half-day min $625.</t>
+          <t>Standard / Same Week / Emergency</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Drives surcharge logic.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Storm cleanup (emergency)</t>
+          <t>Quote Confidence</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>$215 per hour</t>
+          <t>Dropdown</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>4-hour minimum.</t>
+          <t>High / Medium / Low</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>High = remote quote OK; Medium = photos required; Low = site visit.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Suggested Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Driveway</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>All gravel driveway, pothole, and culvert work</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Potholes</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Pothole-only jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Cleanup</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>General property cleanup work</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Storm</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Storm response work</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Brush</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Brush pile removal and brush cutting</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Fence Line</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Fence line cleanup or fence removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Acreage</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Acreage mowing jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Stump</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Stump grinding work</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Tree</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Small tree removal</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Drainage</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Minor drainage correction (specialty)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Acreage mowing</t>
+          <t>Demolition</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>From $195 per acre</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>$450 minimum.</t>
+          <t>Small demolition work</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Heavy brush cutting</t>
+          <t>Recurring</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>$235 per hour</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>$650 minimum.</t>
+          <t>Customer is on a recurring schedule</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Fence line cleanup</t>
+          <t>High Margin</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>From $4.50 per linear foot</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>$750 minimum.</t>
+          <t>Pothole, stump, brush burn, storm — track high-margin jobs</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Stump grinding</t>
+          <t>Emergency</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>$7 per inch of diameter</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>$185 minimum visit.</t>
+          <t>Same-week or 48-hr response</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Small tree removal</t>
+          <t>Bundle</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>From $385 per tree</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Accessible up to 25 ft.</t>
+          <t>Jobs sold as a package</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Light grading</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>$185 per hour</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>4-hour minimum recommended.</t>
+          <t>Rural acreage clients (&gt;25 mi or county addresses)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Dirt work</t>
+          <t>Residential</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>$195 per hour</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>$650 minimum.</t>
+          <t>Residential lots inside city limits</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Minor drainage correction</t>
+          <t>Material Delivery</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>From $1,450</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Quoted per project.</t>
+          <t>Material pass-through included</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Material spreading</t>
+          <t>Recurring Maintenance</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>From $55 per ton or $65 per yard</t>
+          <t>Seasonal maintenance plans (mowing, etc.)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Pricing</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Minimum / Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Gravel driveway repair</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>From $145 per ton applied</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>$650 minimum. AB-3 road base. Tracked Bobcat. Owner-operated. Free quotes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Pothole repair (single)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>$185</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Mobilization-driven minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Pothole repair (2-4 holes)</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>$450</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Most common residential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Pothole repair (5-10 holes)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>$850</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Half-day equivalent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Pothole repair (11-20 holes)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>$1,450</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Includes light grading touch-up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Driveway grading &amp; reshaping</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>$185 per hour</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2-hour minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Driveway culvert repair</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>From $1,650 per project</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>$850 minimum. Half day to full day typical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Acreage mowing</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>From $195 per acre</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>$450 minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Heavy brush cutting</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>$235 per hour</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>$850 minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Fence line cleanup</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>From $4.50 per linear foot</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>$750 minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Brush pile removal</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>From $275 per pile</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Rural burn option from $185.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>General property cleanup</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>$185 per hour</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Half-day min $625.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Storm cleanup (emergency)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>$215 per hour</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4-hour minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Stump grinding</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>$7 per inch of diameter</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>$185 minimum visit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Small tree removal</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>From $385 per tree</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Accessible up to 25 ft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Skid steer hourly</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>$185 per hour</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>2-hour minimum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Half day skid steer</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>$625 flat</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4 hours, mobilization included within 25 mi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Full day skid steer</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>$1,200 flat</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>8 hours, mobilization included within 25 mi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Light grading</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>$185 per hour</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>$450 minimum.</t>
+          <t>4-hour minimum recommended (project work).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Small demolition</t>
+          <t>Dirt work</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>From $850 per project</t>
+          <t>$195 per hour</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Quoted on-site.</t>
+          <t>$650 minimum (project work).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Fence removal</t>
+          <t>Minor drainage correction</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>From $6.50 per linear foot</t>
+          <t>From $1,450</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Includes haul-off.</t>
+          <t>Project work; site visit required.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Skid steer hourly</t>
+          <t>Small demolition</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>$185 per hour</t>
+          <t>From $850 per project</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>2-hour minimum.</t>
+          <t>Quoted on-site.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Half day skid steer</t>
+          <t>Fence removal</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>$625 flat</t>
+          <t>From $6.50 per linear foot</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4 hours, mobilization included within 25 mi.</t>
+          <t>Includes haul-off.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Full day skid steer</t>
+          <t>Rural Property Cleanup Package</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>$1,200 flat</t>
+          <t>$1,495</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>8 hours, mobilization included within 25 mi.</t>
+          <t>Bundle - saves $155.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Rural Property Cleanup Package</t>
+          <t>Driveway Refresh Package</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>$1,495</t>
+          <t>$1,995</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Bundle - saves $155.</t>
+          <t>Bundle - saves $255.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Driveway Refresh Package</t>
+          <t>Storm Cleanup Package</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>$1,995</t>
+          <t>$1,950</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Bundle - saves $255.</t>
+          <t>Bundle - saves $200.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Storm Cleanup Package</t>
+          <t>Fence Line Recovery Package</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>$1,950</t>
+          <t>$4,250</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Bundle - saves $200.</t>
+          <t>Bundle - saves $400.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Fence Line Recovery Package</t>
+          <t>Acreage Maintenance (per visit)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>$4,250</t>
+          <t>$1,375</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Bundle - saves $400.</t>
+          <t>Bundle - per visit.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Acreage Maintenance (per visit)</t>
+          <t>Acreage Maintenance (3-visit season)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>$1,375</t>
+          <t>$3,750</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Bundle - per visit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>Acreage Maintenance (3-visit season)</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>$3,750</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Bundle - saves $375 vs per-visit.</t>
         </is>
